--- a/ns-3.45/result_csv/cu_0125_RSSI.xlsx
+++ b/ns-3.45/result_csv/cu_0125_RSSI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8C5B1EC4-56BA-4D4E-8824-96C75F483C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{431FCD56-64DE-1844-B741-61296D7D2F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9760" yWindow="1760" windowWidth="27900" windowHeight="16860" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t>Stations</t>
   </si>
@@ -1236,7 +1236,534 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Station=15</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>,1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台あたりの</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Load10Mbps</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>の場合</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$S$9:$S$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$I$9:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>86.094399999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.634699999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.571600000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.124600000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88.010099999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>89.343999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>88.967699999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E72B-A94F-A7FD-7AE7255EDF57}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="391486911"/>
+        <c:axId val="391487359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="391486911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>RSSI</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391487359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="391487359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391486911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1792,20 +2319,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>692150</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>234950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>501650</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1825,6 +2868,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{816A9D71-A54D-DB42-84F8-994310B7EFA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2150,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7B48AF-AE98-924B-BFA3-6463D83C2609}">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2647,6 +3728,440 @@
       </c>
       <c r="T8">
         <v>13.6929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
+      <c r="D9">
+        <v>1400</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>65535</v>
+      </c>
+      <c r="H9">
+        <v>65535</v>
+      </c>
+      <c r="I9">
+        <v>86.094399999999993</v>
+      </c>
+      <c r="J9">
+        <v>77.288799999999995</v>
+      </c>
+      <c r="K9">
+        <v>1.2939799999999999</v>
+      </c>
+      <c r="L9">
+        <v>10.183199999999999</v>
+      </c>
+      <c r="M9">
+        <v>38.744700000000002</v>
+      </c>
+      <c r="N9">
+        <v>441405</v>
+      </c>
+      <c r="O9">
+        <v>697861</v>
+      </c>
+      <c r="P9">
+        <v>63.251100000000001</v>
+      </c>
+      <c r="Q9">
+        <v>15</v>
+      </c>
+      <c r="R9">
+        <v>1.41658</v>
+      </c>
+      <c r="S9">
+        <v>-31.677700000000002</v>
+      </c>
+      <c r="T9">
+        <v>57.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>150</v>
+      </c>
+      <c r="D10">
+        <v>1400</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>65535</v>
+      </c>
+      <c r="H10">
+        <v>65535</v>
+      </c>
+      <c r="I10">
+        <v>85.634699999999995</v>
+      </c>
+      <c r="J10">
+        <v>80.592299999999994</v>
+      </c>
+      <c r="K10">
+        <v>1.9201600000000001</v>
+      </c>
+      <c r="L10">
+        <v>11.4032</v>
+      </c>
+      <c r="M10">
+        <v>39.948999999999998</v>
+      </c>
+      <c r="N10">
+        <v>511030</v>
+      </c>
+      <c r="O10">
+        <v>768177</v>
+      </c>
+      <c r="P10">
+        <v>66.525000000000006</v>
+      </c>
+      <c r="Q10">
+        <v>15</v>
+      </c>
+      <c r="R10">
+        <v>1.4671400000000001</v>
+      </c>
+      <c r="S10">
+        <v>-52.646799999999999</v>
+      </c>
+      <c r="T10">
+        <v>36.478400000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>150</v>
+      </c>
+      <c r="D11">
+        <v>1400</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>65535</v>
+      </c>
+      <c r="H11">
+        <v>65535</v>
+      </c>
+      <c r="I11">
+        <v>87.571600000000004</v>
+      </c>
+      <c r="J11">
+        <v>72.556200000000004</v>
+      </c>
+      <c r="K11">
+        <v>1.75309</v>
+      </c>
+      <c r="L11">
+        <v>16.523299999999999</v>
+      </c>
+      <c r="M11">
+        <v>36.578099999999999</v>
+      </c>
+      <c r="N11">
+        <v>394398</v>
+      </c>
+      <c r="O11">
+        <v>683837</v>
+      </c>
+      <c r="P11">
+        <v>57.674300000000002</v>
+      </c>
+      <c r="Q11">
+        <v>15</v>
+      </c>
+      <c r="R11">
+        <v>1.49532</v>
+      </c>
+      <c r="S11">
+        <v>-61.677700000000002</v>
+      </c>
+      <c r="T11">
+        <v>27.7715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>150</v>
+      </c>
+      <c r="D12">
+        <v>1400</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>65535</v>
+      </c>
+      <c r="H12">
+        <v>65535</v>
+      </c>
+      <c r="I12">
+        <v>87.124600000000001</v>
+      </c>
+      <c r="J12">
+        <v>53.523000000000003</v>
+      </c>
+      <c r="K12">
+        <v>1.5777699999999999</v>
+      </c>
+      <c r="L12">
+        <v>23.943999999999999</v>
+      </c>
+      <c r="M12">
+        <v>38.747300000000003</v>
+      </c>
+      <c r="N12">
+        <v>326137</v>
+      </c>
+      <c r="O12">
+        <v>515565</v>
+      </c>
+      <c r="P12">
+        <v>63.258200000000002</v>
+      </c>
+      <c r="Q12">
+        <v>15</v>
+      </c>
+      <c r="R12">
+        <v>1.4755100000000001</v>
+      </c>
+      <c r="S12">
+        <v>-66.960400000000007</v>
+      </c>
+      <c r="T12">
+        <v>22.546700000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>150</v>
+      </c>
+      <c r="D13">
+        <v>1400</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>65535</v>
+      </c>
+      <c r="H13">
+        <v>65535</v>
+      </c>
+      <c r="I13">
+        <v>88.010099999999994</v>
+      </c>
+      <c r="J13">
+        <v>57.395800000000001</v>
+      </c>
+      <c r="K13">
+        <v>1.4099299999999999</v>
+      </c>
+      <c r="L13">
+        <v>19.606999999999999</v>
+      </c>
+      <c r="M13">
+        <v>37.048999999999999</v>
+      </c>
+      <c r="N13">
+        <v>326960</v>
+      </c>
+      <c r="O13">
+        <v>555548</v>
+      </c>
+      <c r="P13">
+        <v>58.8536</v>
+      </c>
+      <c r="Q13">
+        <v>15</v>
+      </c>
+      <c r="R13">
+        <v>1.48851</v>
+      </c>
+      <c r="S13">
+        <v>-70.708600000000004</v>
+      </c>
+      <c r="T13">
+        <v>18.2273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>150</v>
+      </c>
+      <c r="D14">
+        <v>1400</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>65535</v>
+      </c>
+      <c r="H14">
+        <v>65535</v>
+      </c>
+      <c r="I14">
+        <v>89.343999999999994</v>
+      </c>
+      <c r="J14">
+        <v>35.385599999999997</v>
+      </c>
+      <c r="K14">
+        <v>2.63687</v>
+      </c>
+      <c r="L14">
+        <v>42.206499999999998</v>
+      </c>
+      <c r="M14">
+        <v>47.360700000000001</v>
+      </c>
+      <c r="N14">
+        <v>302046</v>
+      </c>
+      <c r="O14">
+        <v>335711</v>
+      </c>
+      <c r="P14">
+        <v>89.971999999999994</v>
+      </c>
+      <c r="Q14">
+        <v>15</v>
+      </c>
+      <c r="R14">
+        <v>1.33026</v>
+      </c>
+      <c r="S14">
+        <v>-73.615899999999996</v>
+      </c>
+      <c r="T14">
+        <v>15.493600000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <v>150</v>
+      </c>
+      <c r="D15">
+        <v>1400</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>65535</v>
+      </c>
+      <c r="H15">
+        <v>65535</v>
+      </c>
+      <c r="I15">
+        <v>88.967699999999994</v>
+      </c>
+      <c r="J15">
+        <v>33.329300000000003</v>
+      </c>
+      <c r="K15">
+        <v>2.64621</v>
+      </c>
+      <c r="L15">
+        <v>39.4358</v>
+      </c>
+      <c r="M15">
+        <v>46.969900000000003</v>
+      </c>
+      <c r="N15">
+        <v>218358</v>
+      </c>
+      <c r="O15">
+        <v>246531</v>
+      </c>
+      <c r="P15">
+        <v>88.572199999999995</v>
+      </c>
+      <c r="Q15">
+        <v>15</v>
+      </c>
+      <c r="R15">
+        <v>1.3136300000000001</v>
+      </c>
+      <c r="S15">
+        <v>-75.991299999999995</v>
+      </c>
+      <c r="T15">
+        <v>13.9893</v>
       </c>
     </row>
   </sheetData>

--- a/ns-3.45/result_csv/cu_0125_RSSI.xlsx
+++ b/ns-3.45/result_csv/cu_0125_RSSI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{431FCD56-64DE-1844-B741-61296D7D2F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A9B525FE-B8CB-B445-9A6F-7B37192D4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9760" yWindow="1760" windowWidth="27900" windowHeight="16860" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="22">
   <si>
     <t>Stations</t>
   </si>
@@ -1695,12 +1695,553 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="5000"/>
+              <a:lumOff val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="74000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="45000"/>
+              <a:lumOff val="55000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="83000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="45000"/>
+              <a:lumOff val="55000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="30000"/>
+              <a:lumOff val="70000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Station=10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>,1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台あたりの</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Load10Mbps</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>の場合</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10557633420822396"/>
+          <c:y val="6.4814814814814811E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$S$16:$S$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$I$16:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>82.222800000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.644900000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.452699999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>81.409300000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85.6648</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87.747799999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>79.426699999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A7DC-7A4A-88BE-29E67CC29D35}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="391486911"/>
+        <c:axId val="391487359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="391486911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>RSSI</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391487359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="391487359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391486911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="5000"/>
+              <a:lumOff val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="74000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="45000"/>
+              <a:lumOff val="55000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="83000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="45000"/>
+              <a:lumOff val="55000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="accent1">
+              <a:lumMod val="30000"/>
+              <a:lumOff val="70000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1803,6 +2344,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2835,20 +3416,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>234950</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>869379</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>98532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>678879</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>47732</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2875,16 +3972,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>736457</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>100173</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>545957</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>49373</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2906,6 +4003,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>749158</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123719</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>558658</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>70065</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="グラフ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9CA1DC1-14DA-384F-8113-FBF505F889FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3231,7 +4366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7B48AF-AE98-924B-BFA3-6463D83C2609}">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -4162,6 +5297,440 @@
       </c>
       <c r="T15">
         <v>13.9893</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>1400</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>65535</v>
+      </c>
+      <c r="H16">
+        <v>65535</v>
+      </c>
+      <c r="I16">
+        <v>82.222800000000007</v>
+      </c>
+      <c r="J16">
+        <v>65.236400000000003</v>
+      </c>
+      <c r="K16">
+        <v>1.5820099999999999</v>
+      </c>
+      <c r="L16">
+        <v>8.3252900000000007</v>
+      </c>
+      <c r="M16">
+        <v>40.654800000000002</v>
+      </c>
+      <c r="N16">
+        <v>457187</v>
+      </c>
+      <c r="O16">
+        <v>667371</v>
+      </c>
+      <c r="P16">
+        <v>68.505700000000004</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16">
+        <v>1.3615900000000001</v>
+      </c>
+      <c r="S16">
+        <v>-31.677700000000002</v>
+      </c>
+      <c r="T16">
+        <v>57.360500000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>1400</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>65535</v>
+      </c>
+      <c r="H17">
+        <v>65535</v>
+      </c>
+      <c r="I17">
+        <v>79.644900000000007</v>
+      </c>
+      <c r="J17">
+        <v>65.7744</v>
+      </c>
+      <c r="K17">
+        <v>1.81464</v>
+      </c>
+      <c r="L17">
+        <v>10.902699999999999</v>
+      </c>
+      <c r="M17">
+        <v>42.767299999999999</v>
+      </c>
+      <c r="N17">
+        <v>511319</v>
+      </c>
+      <c r="O17">
+        <v>684265</v>
+      </c>
+      <c r="P17">
+        <v>74.725300000000004</v>
+      </c>
+      <c r="Q17">
+        <v>15</v>
+      </c>
+      <c r="R17">
+        <v>1.34666</v>
+      </c>
+      <c r="S17">
+        <v>-52.646799999999999</v>
+      </c>
+      <c r="T17">
+        <v>36.332599999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>1400</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>65535</v>
+      </c>
+      <c r="H18">
+        <v>65535</v>
+      </c>
+      <c r="I18">
+        <v>79.452699999999993</v>
+      </c>
+      <c r="J18">
+        <v>62.309800000000003</v>
+      </c>
+      <c r="K18">
+        <v>1.8540399999999999</v>
+      </c>
+      <c r="L18">
+        <v>10.911</v>
+      </c>
+      <c r="M18">
+        <v>40.3489</v>
+      </c>
+      <c r="N18">
+        <v>436713</v>
+      </c>
+      <c r="O18">
+        <v>645629</v>
+      </c>
+      <c r="P18">
+        <v>67.641499999999994</v>
+      </c>
+      <c r="Q18">
+        <v>15</v>
+      </c>
+      <c r="R18">
+        <v>1.36358</v>
+      </c>
+      <c r="S18">
+        <v>-61.677700000000002</v>
+      </c>
+      <c r="T18">
+        <v>27.178799999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <v>1400</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>65535</v>
+      </c>
+      <c r="H19">
+        <v>65535</v>
+      </c>
+      <c r="I19">
+        <v>81.409300000000002</v>
+      </c>
+      <c r="J19">
+        <v>60.837699999999998</v>
+      </c>
+      <c r="K19">
+        <v>1.6180600000000001</v>
+      </c>
+      <c r="L19">
+        <v>11.1221</v>
+      </c>
+      <c r="M19">
+        <v>38.647199999999998</v>
+      </c>
+      <c r="N19">
+        <v>392984</v>
+      </c>
+      <c r="O19">
+        <v>623867</v>
+      </c>
+      <c r="P19">
+        <v>62.991599999999998</v>
+      </c>
+      <c r="Q19">
+        <v>15</v>
+      </c>
+      <c r="R19">
+        <v>1.4201699999999999</v>
+      </c>
+      <c r="S19">
+        <v>-66.960400000000007</v>
+      </c>
+      <c r="T19">
+        <v>22.5106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>1400</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>65535</v>
+      </c>
+      <c r="H20">
+        <v>65535</v>
+      </c>
+      <c r="I20">
+        <v>85.6648</v>
+      </c>
+      <c r="J20">
+        <v>53.711799999999997</v>
+      </c>
+      <c r="K20">
+        <v>1.6702900000000001</v>
+      </c>
+      <c r="L20">
+        <v>18.709099999999999</v>
+      </c>
+      <c r="M20">
+        <v>37.489100000000001</v>
+      </c>
+      <c r="N20">
+        <v>318616</v>
+      </c>
+      <c r="O20">
+        <v>531274</v>
+      </c>
+      <c r="P20">
+        <v>59.972099999999998</v>
+      </c>
+      <c r="Q20">
+        <v>15</v>
+      </c>
+      <c r="R20">
+        <v>1.43398</v>
+      </c>
+      <c r="S20">
+        <v>-70.708600000000004</v>
+      </c>
+      <c r="T20">
+        <v>18.5749</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>1400</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>65535</v>
+      </c>
+      <c r="H21">
+        <v>65535</v>
+      </c>
+      <c r="I21">
+        <v>87.747799999999998</v>
+      </c>
+      <c r="J21">
+        <v>40.662500000000001</v>
+      </c>
+      <c r="K21">
+        <v>2.2276600000000002</v>
+      </c>
+      <c r="L21">
+        <v>27.625299999999999</v>
+      </c>
+      <c r="M21">
+        <v>42.465800000000002</v>
+      </c>
+      <c r="N21">
+        <v>273368</v>
+      </c>
+      <c r="O21">
+        <v>370369</v>
+      </c>
+      <c r="P21">
+        <v>73.809600000000003</v>
+      </c>
+      <c r="Q21">
+        <v>15</v>
+      </c>
+      <c r="R21">
+        <v>1.3749899999999999</v>
+      </c>
+      <c r="S21">
+        <v>-73.615899999999996</v>
+      </c>
+      <c r="T21">
+        <v>15.8627</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>1400</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>65535</v>
+      </c>
+      <c r="H22">
+        <v>65535</v>
+      </c>
+      <c r="I22">
+        <v>79.426699999999997</v>
+      </c>
+      <c r="J22">
+        <v>33.785299999999999</v>
+      </c>
+      <c r="K22">
+        <v>1.7783800000000001</v>
+      </c>
+      <c r="L22">
+        <v>26.411100000000001</v>
+      </c>
+      <c r="M22">
+        <v>46.264000000000003</v>
+      </c>
+      <c r="N22">
+        <v>265621</v>
+      </c>
+      <c r="O22">
+        <v>308521</v>
+      </c>
+      <c r="P22">
+        <v>86.094899999999996</v>
+      </c>
+      <c r="Q22">
+        <v>15</v>
+      </c>
+      <c r="R22">
+        <v>1.1953</v>
+      </c>
+      <c r="S22">
+        <v>-75.991299999999995</v>
+      </c>
+      <c r="T22">
+        <v>12.5489</v>
       </c>
     </row>
   </sheetData>

--- a/ns-3.45/result_csv/cu_0125_RSSI.xlsx
+++ b/ns-3.45/result_csv/cu_0125_RSSI.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A9B525FE-B8CB-B445-9A6F-7B37192D4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{75204CF4-D2BE-C148-9FCA-F7270491EF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9760" yWindow="1760" windowWidth="27900" windowHeight="16860" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
   </bookViews>
   <sheets>
     <sheet name="cu_0125_RSSI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="22">
   <si>
     <t>Stations</t>
   </si>
@@ -1071,6 +1084,7 @@
         <c:axId val="391487359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1558,6 +1572,7 @@
         <c:axId val="391487359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2076,6 +2091,7 @@
         <c:axId val="391487359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2264,6 +2280,982 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Station=1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>,1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台あたりの</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Load10Mbps</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>の場合</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$S$23:$S$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$I$24:$I$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>17.9147</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.872900000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.896699999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.2636</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.315200000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31.885899999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>61.0396</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-407D-9744-9ABF-C67F6B1E8B55}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="391486911"/>
+        <c:axId val="391487359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="391486911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>RSSI</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391487359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="391487359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391486911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Station=5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>,1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>台あたりの</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Load10Mbps</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>の場合</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$S$30:$S$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_RSSI!$I$29:$I$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>31.885899999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61.0396</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>62.106400000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.084699999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.062799999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70.448599999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74.495599999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-ECF9-9D44-BCC3-CAE82E97DDB9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="391486911"/>
+        <c:axId val="391487359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="391486911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>RSSI</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391487359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="391487359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="391486911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2384,6 +3376,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3417,6 +4489,1038 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3937,15 +6041,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>869379</xdr:colOff>
+      <xdr:colOff>897918</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>98532</xdr:rowOff>
+      <xdr:rowOff>184150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>678879</xdr:colOff>
+      <xdr:colOff>707418</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>47732</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3973,15 +6077,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>736457</xdr:colOff>
+      <xdr:colOff>764996</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>100173</xdr:rowOff>
+      <xdr:rowOff>185791</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>545957</xdr:colOff>
+      <xdr:colOff>574496</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>49373</xdr:rowOff>
+      <xdr:rowOff>134991</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4011,15 +6115,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>749158</xdr:colOff>
+      <xdr:colOff>777697</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>123719</xdr:rowOff>
+      <xdr:rowOff>209337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>558658</xdr:colOff>
+      <xdr:colOff>587197</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>70065</xdr:rowOff>
+      <xdr:rowOff>155683</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4041,6 +6145,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>898987</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57079</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>708487</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>6279</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="グラフ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B1D6437-99CF-344F-91D7-ED04B5DFDB77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>827641</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>637141</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>63357</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="グラフ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{191309BD-8802-7347-B54A-4AE5FF5DC5CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4366,7 +6546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7B48AF-AE98-924B-BFA3-6463D83C2609}">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -5731,6 +7911,874 @@
       </c>
       <c r="T22">
         <v>12.5489</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>1400</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>65535</v>
+      </c>
+      <c r="H23">
+        <v>65535</v>
+      </c>
+      <c r="I23">
+        <v>17.889199999999999</v>
+      </c>
+      <c r="J23">
+        <v>11.111800000000001</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>7.0838899999999996E-2</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>116881</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23">
+        <v>1.19435</v>
+      </c>
+      <c r="S23">
+        <v>-31.677700000000002</v>
+      </c>
+      <c r="T23">
+        <v>56.280099999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>1400</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>65535</v>
+      </c>
+      <c r="H24">
+        <v>65535</v>
+      </c>
+      <c r="I24">
+        <v>17.9147</v>
+      </c>
+      <c r="J24">
+        <v>11.111800000000001</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>7.1170600000000001E-2</v>
+      </c>
+      <c r="M24">
+        <v>7.7796400000000002E-2</v>
+      </c>
+      <c r="N24">
+        <v>91</v>
+      </c>
+      <c r="O24">
+        <v>116881</v>
+      </c>
+      <c r="P24">
+        <v>7.7856999999999996E-2</v>
+      </c>
+      <c r="Q24">
+        <v>15</v>
+      </c>
+      <c r="R24">
+        <v>1.19272</v>
+      </c>
+      <c r="S24">
+        <v>-52.646799999999999</v>
+      </c>
+      <c r="T24">
+        <v>35.311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>1400</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>65535</v>
+      </c>
+      <c r="H25">
+        <v>65535</v>
+      </c>
+      <c r="I25">
+        <v>19.872900000000001</v>
+      </c>
+      <c r="J25">
+        <v>11.111800000000001</v>
+      </c>
+      <c r="K25">
+        <v>3.8501999999999998E-3</v>
+      </c>
+      <c r="L25">
+        <v>9.1720099999999999E-2</v>
+      </c>
+      <c r="M25">
+        <v>4.9609300000000003</v>
+      </c>
+      <c r="N25">
+        <v>6101</v>
+      </c>
+      <c r="O25">
+        <v>116880</v>
+      </c>
+      <c r="P25">
+        <v>5.2198799999999999</v>
+      </c>
+      <c r="Q25">
+        <v>15</v>
+      </c>
+      <c r="R25">
+        <v>1.15334</v>
+      </c>
+      <c r="S25">
+        <v>-61.677700000000002</v>
+      </c>
+      <c r="T25">
+        <v>26.292000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>1400</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>65535</v>
+      </c>
+      <c r="H26">
+        <v>65535</v>
+      </c>
+      <c r="I26">
+        <v>17.896699999999999</v>
+      </c>
+      <c r="J26">
+        <v>9.9104600000000005</v>
+      </c>
+      <c r="K26">
+        <v>4.3195300000000002E-3</v>
+      </c>
+      <c r="L26">
+        <v>0.10072</v>
+      </c>
+      <c r="M26">
+        <v>6.1093500000000001</v>
+      </c>
+      <c r="N26">
+        <v>6779</v>
+      </c>
+      <c r="O26">
+        <v>104182</v>
+      </c>
+      <c r="P26">
+        <v>6.5068799999999998</v>
+      </c>
+      <c r="Q26">
+        <v>15</v>
+      </c>
+      <c r="R26">
+        <v>1.14818</v>
+      </c>
+      <c r="S26">
+        <v>-66.960400000000007</v>
+      </c>
+      <c r="T26">
+        <v>21.026599999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>1400</v>
+      </c>
+      <c r="E27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>65535</v>
+      </c>
+      <c r="H27">
+        <v>65535</v>
+      </c>
+      <c r="I27">
+        <v>20.2636</v>
+      </c>
+      <c r="J27">
+        <v>9.9193300000000004</v>
+      </c>
+      <c r="K27">
+        <v>4.3161099999999997E-3</v>
+      </c>
+      <c r="L27">
+        <v>0.13558200000000001</v>
+      </c>
+      <c r="M27">
+        <v>9.8646200000000004</v>
+      </c>
+      <c r="N27">
+        <v>11411</v>
+      </c>
+      <c r="O27">
+        <v>104265</v>
+      </c>
+      <c r="P27">
+        <v>10.9442</v>
+      </c>
+      <c r="Q27">
+        <v>15</v>
+      </c>
+      <c r="R27">
+        <v>1.08782</v>
+      </c>
+      <c r="S27">
+        <v>-70.708600000000004</v>
+      </c>
+      <c r="T27">
+        <v>17.309999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>1400</v>
+      </c>
+      <c r="E28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>65535</v>
+      </c>
+      <c r="H28">
+        <v>65535</v>
+      </c>
+      <c r="I28">
+        <v>22.315200000000001</v>
+      </c>
+      <c r="J28">
+        <v>10.688499999999999</v>
+      </c>
+      <c r="K28">
+        <v>4.0051799999999997E-3</v>
+      </c>
+      <c r="L28">
+        <v>0.13200899999999999</v>
+      </c>
+      <c r="M28">
+        <v>8.2723800000000001</v>
+      </c>
+      <c r="N28">
+        <v>10133</v>
+      </c>
+      <c r="O28">
+        <v>112359</v>
+      </c>
+      <c r="P28">
+        <v>9.0184099999999994</v>
+      </c>
+      <c r="Q28">
+        <v>15</v>
+      </c>
+      <c r="R28">
+        <v>1.13229</v>
+      </c>
+      <c r="S28">
+        <v>-73.615899999999996</v>
+      </c>
+      <c r="T28">
+        <v>14.409800000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>30</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>1400</v>
+      </c>
+      <c r="E29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>65535</v>
+      </c>
+      <c r="H29">
+        <v>65535</v>
+      </c>
+      <c r="I29">
+        <v>31.885899999999999</v>
+      </c>
+      <c r="J29">
+        <v>10.6883</v>
+      </c>
+      <c r="K29">
+        <v>4.0052300000000002E-3</v>
+      </c>
+      <c r="L29">
+        <v>0.418215</v>
+      </c>
+      <c r="M29">
+        <v>32.483899999999998</v>
+      </c>
+      <c r="N29">
+        <v>54058</v>
+      </c>
+      <c r="O29">
+        <v>112357</v>
+      </c>
+      <c r="P29">
+        <v>48.112699999999997</v>
+      </c>
+      <c r="Q29">
+        <v>15</v>
+      </c>
+      <c r="R29">
+        <v>0.83440800000000004</v>
+      </c>
+      <c r="S29">
+        <v>-75.991299999999995</v>
+      </c>
+      <c r="T29">
+        <v>12.049200000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>1400</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>65535</v>
+      </c>
+      <c r="H30">
+        <v>65535</v>
+      </c>
+      <c r="I30">
+        <v>61.0396</v>
+      </c>
+      <c r="J30">
+        <v>52.073300000000003</v>
+      </c>
+      <c r="K30">
+        <v>0.440606</v>
+      </c>
+      <c r="L30">
+        <v>2.87819</v>
+      </c>
+      <c r="M30">
+        <v>43.4069</v>
+      </c>
+      <c r="N30">
+        <v>432748</v>
+      </c>
+      <c r="O30">
+        <v>564209</v>
+      </c>
+      <c r="P30">
+        <v>76.6999</v>
+      </c>
+      <c r="Q30">
+        <v>15</v>
+      </c>
+      <c r="R30">
+        <v>1.08772</v>
+      </c>
+      <c r="S30">
+        <v>-31.677700000000002</v>
+      </c>
+      <c r="T30">
+        <v>56.6783</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>50</v>
+      </c>
+      <c r="D31">
+        <v>1400</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>65535</v>
+      </c>
+      <c r="H31">
+        <v>65535</v>
+      </c>
+      <c r="I31">
+        <v>62.106400000000001</v>
+      </c>
+      <c r="J31">
+        <v>51.853000000000002</v>
+      </c>
+      <c r="K31">
+        <v>0.52671400000000002</v>
+      </c>
+      <c r="L31">
+        <v>3.31833</v>
+      </c>
+      <c r="M31">
+        <v>41.530700000000003</v>
+      </c>
+      <c r="N31">
+        <v>398720</v>
+      </c>
+      <c r="O31">
+        <v>561342</v>
+      </c>
+      <c r="P31">
+        <v>71.029799999999994</v>
+      </c>
+      <c r="Q31">
+        <v>15</v>
+      </c>
+      <c r="R31">
+        <v>1.13235</v>
+      </c>
+      <c r="S31">
+        <v>-52.646799999999999</v>
+      </c>
+      <c r="T31">
+        <v>35.781799999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>1400</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>65535</v>
+      </c>
+      <c r="H32">
+        <v>65535</v>
+      </c>
+      <c r="I32">
+        <v>65.084699999999998</v>
+      </c>
+      <c r="J32">
+        <v>50.895000000000003</v>
+      </c>
+      <c r="K32">
+        <v>0.59647899999999998</v>
+      </c>
+      <c r="L32">
+        <v>4.1460800000000004</v>
+      </c>
+      <c r="M32">
+        <v>41.771900000000002</v>
+      </c>
+      <c r="N32">
+        <v>393047</v>
+      </c>
+      <c r="O32">
+        <v>547890</v>
+      </c>
+      <c r="P32">
+        <v>71.738299999999995</v>
+      </c>
+      <c r="Q32">
+        <v>15</v>
+      </c>
+      <c r="R32">
+        <v>1.17058</v>
+      </c>
+      <c r="S32">
+        <v>-61.677700000000002</v>
+      </c>
+      <c r="T32">
+        <v>26.767399999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>50</v>
+      </c>
+      <c r="D33">
+        <v>1400</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>65535</v>
+      </c>
+      <c r="H33">
+        <v>65535</v>
+      </c>
+      <c r="I33">
+        <v>67.062799999999996</v>
+      </c>
+      <c r="J33">
+        <v>51.606299999999997</v>
+      </c>
+      <c r="K33">
+        <v>0.84463200000000005</v>
+      </c>
+      <c r="L33">
+        <v>3.7194199999999999</v>
+      </c>
+      <c r="M33">
+        <v>40.8127</v>
+      </c>
+      <c r="N33">
+        <v>369837</v>
+      </c>
+      <c r="O33">
+        <v>536344</v>
+      </c>
+      <c r="P33">
+        <v>68.955200000000005</v>
+      </c>
+      <c r="Q33">
+        <v>15</v>
+      </c>
+      <c r="R33">
+        <v>1.1847000000000001</v>
+      </c>
+      <c r="S33">
+        <v>-66.960400000000007</v>
+      </c>
+      <c r="T33">
+        <v>21.512799999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>50</v>
+      </c>
+      <c r="D34">
+        <v>1400</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>65535</v>
+      </c>
+      <c r="H34">
+        <v>65535</v>
+      </c>
+      <c r="I34">
+        <v>70.448599999999999</v>
+      </c>
+      <c r="J34">
+        <v>46.617400000000004</v>
+      </c>
+      <c r="K34">
+        <v>0.792014</v>
+      </c>
+      <c r="L34">
+        <v>4.2477200000000002</v>
+      </c>
+      <c r="M34">
+        <v>41.978400000000001</v>
+      </c>
+      <c r="N34">
+        <v>360064</v>
+      </c>
+      <c r="O34">
+        <v>497673</v>
+      </c>
+      <c r="P34">
+        <v>72.349500000000006</v>
+      </c>
+      <c r="Q34">
+        <v>15</v>
+      </c>
+      <c r="R34">
+        <v>1.1776199999999999</v>
+      </c>
+      <c r="S34">
+        <v>-70.708600000000004</v>
+      </c>
+      <c r="T34">
+        <v>17.877500000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35">
+        <v>25</v>
+      </c>
+      <c r="C35">
+        <v>50</v>
+      </c>
+      <c r="D35">
+        <v>1400</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>65535</v>
+      </c>
+      <c r="H35">
+        <v>65535</v>
+      </c>
+      <c r="I35">
+        <v>74.495599999999996</v>
+      </c>
+      <c r="J35">
+        <v>44.956400000000002</v>
+      </c>
+      <c r="K35">
+        <v>0.87380899999999995</v>
+      </c>
+      <c r="L35">
+        <v>4.7923400000000003</v>
+      </c>
+      <c r="M35">
+        <v>38.633200000000002</v>
+      </c>
+      <c r="N35">
+        <v>290987</v>
+      </c>
+      <c r="O35">
+        <v>462217</v>
+      </c>
+      <c r="P35">
+        <v>62.954599999999999</v>
+      </c>
+      <c r="Q35">
+        <v>15</v>
+      </c>
+      <c r="R35">
+        <v>1.22987</v>
+      </c>
+      <c r="S35">
+        <v>-73.615899999999996</v>
+      </c>
+      <c r="T35">
+        <v>15.129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>50</v>
+      </c>
+      <c r="D36">
+        <v>1400</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>65535</v>
+      </c>
+      <c r="H36">
+        <v>65535</v>
+      </c>
+      <c r="I36">
+        <v>65.202600000000004</v>
+      </c>
+      <c r="J36">
+        <v>29.0641</v>
+      </c>
+      <c r="K36">
+        <v>1.0196499999999999</v>
+      </c>
+      <c r="L36">
+        <v>8.5613200000000003</v>
+      </c>
+      <c r="M36">
+        <v>40.9497</v>
+      </c>
+      <c r="N36">
+        <v>211237</v>
+      </c>
+      <c r="O36">
+        <v>304608</v>
+      </c>
+      <c r="P36">
+        <v>69.347200000000001</v>
+      </c>
+      <c r="Q36">
+        <v>15</v>
+      </c>
+      <c r="R36">
+        <v>1.1843600000000001</v>
+      </c>
+      <c r="S36">
+        <v>-75.991299999999995</v>
+      </c>
+      <c r="T36">
+        <v>12.258100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ns-3.45/result_csv/cu_0125_RSSI.xlsx
+++ b/ns-3.45/result_csv/cu_0125_RSSI.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawamasahiro/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6550BF21-7F8D-D94A-9345-FFCD283ADDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC7465D-3C86-A94D-BE93-81AB4D7588E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9760" yWindow="1760" windowWidth="27900" windowHeight="16860" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
+    <workbookView xWindow="600" yWindow="600" windowWidth="27900" windowHeight="16180" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
   </bookViews>
   <sheets>
     <sheet name="cu_0125_RSSI" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cu_0125_RSSI!$A$1:$T$85</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">cu_0125_RSSI!$I$16:$I$22</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">cu_0125_RSSI!$I$23:$I$29</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">cu_0125_RSSI!$S$51:$S$57</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">cu_0125_RSSI!$I$2:$I$8</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">cu_0125_RSSI!$I$30:$I$36</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">cu_0125_RSSI!$I$37:$I$43</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">cu_0125_RSSI!$I$44:$I$50</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">cu_0125_RSSI!$I$51:$I$57</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">cu_0125_RSSI!$I$9:$I$15</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">cu_0125_RSSI!$S$16:$S$22</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">cu_0125_RSSI!$S$2:$S$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -793,28 +782,18 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:rPr lang="en-US"/>
               <a:t>RSSI</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:rPr lang="ja-JP"/>
               <a:t>の場合</a:t>
             </a:r>
           </a:p>
@@ -1517,27 +1496,17 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:rPr lang="en-US"/>
                   <a:t>RSSI</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1568,21 +1537,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -1615,24 +1574,14 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:rPr lang="ja-JP"/>
                   <a:t>チャネル使用率</a:t>
                 </a:r>
               </a:p>
@@ -1665,21 +1614,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -1713,7 +1652,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1800"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -1743,28 +1682,18 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:rPr lang="en-US"/>
               <a:t>SNR</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:rPr lang="ja-JP"/>
               <a:t>の場合</a:t>
             </a:r>
           </a:p>
@@ -2443,27 +2372,17 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>RSSI</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SNR</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2494,21 +2413,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -2541,24 +2450,14 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:rPr lang="ja-JP"/>
                   <a:t>チャネル使用率</a:t>
                 </a:r>
               </a:p>
@@ -2591,21 +2490,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -2617,6 +2506,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13370692462862144"/>
+          <c:y val="9.7200303561835816E-2"/>
+          <c:w val="0.71201491125615879"/>
+          <c:h val="5.2896522196141944E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2639,7 +2538,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1400"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -2669,24 +2568,14 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:rPr lang="ja-JP"/>
               <a:t>再送率の場合</a:t>
             </a:r>
           </a:p>
@@ -2718,6 +2607,9 @@
         <c:ser>
           <c:idx val="4"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>N=1</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100">
               <a:noFill/>
@@ -2793,6 +2685,9 @@
         <c:ser>
           <c:idx val="7"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>N=2</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -2870,6 +2765,9 @@
         <c:ser>
           <c:idx val="5"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:v>N=3</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -2947,6 +2845,9 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:tx>
+            <c:v>N=4</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -3024,6 +2925,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="4"/>
+          <c:tx>
+            <c:v>N=5</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -3116,6 +3020,9 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="5"/>
+          <c:tx>
+            <c:v>N=6</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100">
               <a:noFill/>
@@ -3191,6 +3098,9 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="6"/>
+          <c:tx>
+            <c:v>N=7</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100">
               <a:noFill/>
@@ -3266,6 +3176,9 @@
         <c:ser>
           <c:idx val="6"/>
           <c:order val="7"/>
+          <c:tx>
+            <c:v>N=8</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100">
               <a:noFill/>
@@ -3373,27 +3286,16 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>RSSI</a:t>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>再送率</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -3424,21 +3326,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -3471,24 +3363,14 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:rPr lang="ja-JP"/>
                   <a:t>チャネル使用率</a:t>
                 </a:r>
               </a:p>
@@ -3521,21 +3403,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -3569,7 +3441,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1600"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -3586,16 +3458,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>146977</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>205196</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>603606</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>105309</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>185505</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>57078</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>670674</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>156967</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3622,16 +3494,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>513707</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>57079</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>907444</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>156791</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>552235</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>165814</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>721235</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>164228</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3660,16 +3532,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>371011</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>85617</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>363612</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>172643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>409540</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>402141</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>194352</xdr:rowOff>
+      <xdr:rowOff>243993</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
